--- a/Attendance roster_Splunk Basic_23-24 March_.xlsx
+++ b/Attendance roster_Splunk Basic_23-24 March_.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\VK_GIT\SPLK_CISCO_INDIA_23_03_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8880BD0-C99D-4D99-9D19-0DF8C6198ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9BF329-49DF-42FA-9D96-258E36B2AF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="50">
   <si>
     <t>Start Date</t>
   </si>
@@ -170,6 +170,12 @@
   </si>
   <si>
     <t>Password</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -641,24 +647,24 @@
     <xf numFmtId="15" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -951,10 +957,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="26"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1038,8 +1044,12 @@
       <c r="B12" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12"/>
+      <c r="C12" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
@@ -1048,8 +1058,12 @@
       <c r="B13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="15"/>
+      <c r="C13" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
@@ -1058,8 +1072,12 @@
       <c r="B14" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="15"/>
+      <c r="C14" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
@@ -1068,8 +1086,12 @@
       <c r="B15" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="15"/>
+      <c r="C15" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
@@ -1078,8 +1100,12 @@
       <c r="B16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="15"/>
+      <c r="C16" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
@@ -1088,8 +1114,12 @@
       <c r="B17" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="15"/>
+      <c r="C17" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
@@ -1098,8 +1128,12 @@
       <c r="B18" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
+      <c r="C18" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
@@ -1108,8 +1142,12 @@
       <c r="B19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="15"/>
+      <c r="C19" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
@@ -1118,8 +1156,12 @@
       <c r="B20" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="15"/>
+      <c r="C20" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
@@ -1128,8 +1170,12 @@
       <c r="B21" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
+      <c r="C21" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
@@ -1138,8 +1184,12 @@
       <c r="B22" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
+      <c r="C22" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18" t="s">
@@ -1148,8 +1198,12 @@
       <c r="B23" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="20"/>
+      <c r="C23" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1174,44 +1228,44 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="25" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D10" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1222,10 +1276,10 @@
       <c r="C11" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="29" t="s">
+      <c r="D11" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1236,10 +1290,10 @@
       <c r="C12" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="29" t="s">
+      <c r="D12" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1250,10 +1304,10 @@
       <c r="C13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1264,10 +1318,10 @@
       <c r="C14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="30" t="s">
+      <c r="E14" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1278,10 +1332,10 @@
       <c r="C15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="E15" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1292,10 +1346,10 @@
       <c r="C16" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="29" t="s">
+      <c r="D16" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="E16" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1306,10 +1360,10 @@
       <c r="C17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="E17" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1320,10 +1374,10 @@
       <c r="C18" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="E18" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1334,10 +1388,10 @@
       <c r="C19" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E19" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1348,10 +1402,10 @@
       <c r="C20" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="28" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1362,10 +1416,10 @@
       <c r="C21" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="E21" s="28" t="s">
         <v>34</v>
       </c>
     </row>
